--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:35</t>
+    <t xml:space="preserve">2026-09-09 22:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:20</t>
+    <t xml:space="preserve">2026-09-12 19:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:37</t>
+    <t xml:space="preserve">2026-09-24 00:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:14</t>
+    <t xml:space="preserve">2026-09-27 22:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:04</t>
+    <t xml:space="preserve">2026-09-29 10:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -502,7 +502,7 @@
         <v>2019</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>38.06</v>
+        <v>380.63</v>
       </c>
     </row>
     <row r="3">
@@ -519,7 +519,7 @@
         <v>2019</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>23.4</v>
+        <v>233.96</v>
       </c>
     </row>
     <row r="4">
@@ -536,7 +536,7 @@
         <v>2019</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>20.7</v>
+        <v>207.03</v>
       </c>
     </row>
     <row r="5">
@@ -553,7 +553,7 @@
         <v>2019</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>15.17</v>
+        <v>151.74</v>
       </c>
     </row>
     <row r="6">
@@ -570,7 +570,7 @@
         <v>2019</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>14.59</v>
+        <v>145.94</v>
       </c>
     </row>
     <row r="7">
@@ -587,7 +587,7 @@
         <v>2019</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>14.06</v>
+        <v>140.64</v>
       </c>
     </row>
     <row r="8">
@@ -604,7 +604,7 @@
         <v>2019</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>11.32</v>
+        <v>113.25</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 10:58</t>
+    <t xml:space="preserve">2026-10-01 19:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:23</t>
+    <t xml:space="preserve">2026-10-02 13:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:03</t>
+    <t xml:space="preserve">2026-10-05 07:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
